--- a/data/ams_weekly_data/White_Mulberry/ads_report_week19.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week19.xlsx
@@ -4238,23 +4238,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2312</v>
+        <v>4624</v>
       </c>
       <c r="E2" t="n">
-        <v>87.5</v>
+        <v>175</v>
       </c>
       <c r="F2" t="n">
-        <v>206.98</v>
+        <v>413.96</v>
       </c>
       <c r="G2" t="n">
-        <v>3380.93</v>
+        <v>6761.86</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4266,28 +4266,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2312</v>
+        <v>4836</v>
       </c>
       <c r="E3" t="n">
-        <v>87.5</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>206.98</v>
+        <v>562.0833333333334</v>
       </c>
       <c r="G3" t="n">
-        <v>3380.93</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4304,14 +4304,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4835.666666666667</v>
+        <v>4836</v>
       </c>
       <c r="E4" t="n">
-        <v>65.33333333333333</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
         <v>562.0833333333334</v>
@@ -4337,14 +4337,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4835.666666666667</v>
+        <v>4836</v>
       </c>
       <c r="E5" t="n">
-        <v>65.33333333333333</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
         <v>562.0833333333334</v>
@@ -4365,28 +4365,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4835.666666666667</v>
+        <v>5593</v>
       </c>
       <c r="E6" t="n">
-        <v>65.33333333333333</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
-        <v>562.0833333333334</v>
+        <v>641.02</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>6807.64</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -4398,28 +4398,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5593</v>
+        <v>11693</v>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>133</v>
       </c>
       <c r="F7" t="n">
-        <v>641.02</v>
+        <v>2153.45</v>
       </c>
       <c r="G7" t="n">
-        <v>6807.64</v>
+        <v>15884.76</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -4431,28 +4431,28 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11693</v>
+        <v>25347</v>
       </c>
       <c r="E8" t="n">
-        <v>133</v>
+        <v>202</v>
       </c>
       <c r="F8" t="n">
-        <v>2153.45</v>
+        <v>2753.100197868014</v>
       </c>
       <c r="G8" t="n">
-        <v>15884.76</v>
+        <v>11521.18</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -4469,23 +4469,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28328</v>
+        <v>2981</v>
       </c>
       <c r="E9" t="n">
-        <v>226</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>3076.91</v>
+        <v>323.8098021319855</v>
       </c>
       <c r="G9" t="n">
-        <v>12876.26</v>
+        <v>1355.08</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week19.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week19.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
